--- a/public/templates/examples/A-035-AccessEntitlementMatrix-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-035-AccessEntitlementMatrix-EXAMPLE-S.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="0"/>
   <fonts count="9">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -313,7 +313,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1619250" cy="1619250"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -427,12 +427,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-035-AccessEntitlementMatrix-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-035-AccessEntitlementMatrix-EXAMPLE-S.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="Aptos"/>
@@ -174,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -227,6 +229,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,7 +683,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="8" t="n"/>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="66.4" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Each row is one authorized grant: a role or vendor type paired with a system or data set and the access level allowed. The matrix is role-indexed; it states what each role may access, not who holds the role. The person-to-role assignment lives in the Account-to-Role Assignment Register, and reconciliation against live accounts is evidenced in the Privilege Review Records and Periodic Account Review / Certification Records.</t>
@@ -719,7 +727,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Director</t>
@@ -740,13 +748,11 @@
           <t>Approved by county; reviewed for least privilege</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
+      <c r="E18" s="21">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Lead Dispatcher</t>
@@ -767,13 +773,11 @@
           <t>Standard dispatcher role</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
+      <c r="E19" s="21">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -794,13 +798,11 @@
           <t>Standard dispatcher role</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
+      <c r="E20" s="21">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>County IT</t>
@@ -821,13 +823,11 @@
           <t>Infrastructure only; no CAD case data</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
+      <c r="E21" s="21">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>CAD vendor (support)</t>
@@ -848,14 +848,12 @@
           <t>Enabled only during a scheduled support window</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="11" t="n"/>
+      <c r="E22" s="21">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23"/>
       <c r="B23" s="12" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="12" t="n"/>
@@ -885,7 +883,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
+    <row r="30" ht="34.7" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Reviewed at least quarterly by the Director, and reconciled against active accounts each cycle. Update on any role or system change.</t>
@@ -966,10 +964,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
+      <c r="B42" s="22">
+        <v>46068</v>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
@@ -983,11 +979,11 @@
       </c>
       <c r="E42" s="14" t="n"/>
     </row>
-    <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="2" t="n"/>
+    <row r="44">
+      <c r="A44"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A15:E15"/>
@@ -1015,12 +1011,11 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>